--- a/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:42</t>
+    <t xml:space="preserve">2026-09-10 00:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:51</t>
+    <t xml:space="preserve">2026-09-18 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:00</t>
+    <t xml:space="preserve">2026-09-23 14:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:21</t>
+    <t xml:space="preserve">2026-10-02 15:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Hualpén</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Lebu</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Santa Juana</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:22</t>
+    <t xml:space="preserve">2026-10-04 10:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:04</t>
+    <t xml:space="preserve">2026-10-05 14:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
